--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7773373-CF22-480D-B2F6-116B40F62CFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76955B7E-4F13-4D22-9A39-F067014975A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -392,51 +392,185 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -444,140 +578,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="7" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1014,600 +1014,600 @@
   <sheetData>
     <row r="2" spans="1:11" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="1"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
     </row>
     <row r="3" spans="1:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>31</v>
       </c>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="H4" s="9" t="s">
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="H4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>2025</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>2026</v>
       </c>
-      <c r="K4" s="11"/>
+      <c r="K4" s="10"/>
     </row>
     <row r="5" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="13">
-        <v>15</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="H5" s="14" t="s">
+      <c r="C5" s="12">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="H5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="15">
-        <v>664887</v>
-      </c>
-      <c r="J5" s="15">
-        <v>496587</v>
-      </c>
-      <c r="K5" s="11"/>
+      <c r="I5" s="14">
+        <v>699546</v>
+      </c>
+      <c r="J5" s="14">
+        <v>540298</v>
+      </c>
+      <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="H6" s="16" t="s">
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="H6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.25312571910715653</v>
-      </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="11"/>
+        <v>-0.22764478676169975</v>
+      </c>
+      <c r="J6" s="57"/>
+      <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="19" t="s">
+      <c r="C7" s="60"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="20"/>
-      <c r="H7" s="9" t="s">
+      <c r="F7" s="60"/>
+      <c r="H7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>2025</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>2026</v>
       </c>
-      <c r="K7" s="11"/>
+      <c r="K7" s="10"/>
     </row>
     <row r="8" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <v>3000000</v>
       </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="14" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="16">
         <f>C8/C$4</f>
         <v>96774.193548387091</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="15">
-        <v>758392</v>
-      </c>
-      <c r="J8" s="15">
-        <v>777363</v>
-      </c>
-      <c r="K8" s="11"/>
+      <c r="I8" s="14">
+        <v>809639</v>
+      </c>
+      <c r="J8" s="14">
+        <v>792644</v>
+      </c>
+      <c r="K8" s="10"/>
     </row>
     <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="18">
         <v>1.8</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="22" t="s">
+      <c r="D9" s="7"/>
+      <c r="E9" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="19">
         <f>C9</f>
         <v>1.8</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>2.5014768088271078E-2</v>
-      </c>
-      <c r="J9" s="18"/>
-      <c r="K9" s="11"/>
+        <v>-2.0990836656830991E-2</v>
+      </c>
+      <c r="J9" s="57"/>
+      <c r="K9" s="10"/>
     </row>
     <row r="10" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="20">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="14" t="s">
+      <c r="D10" s="7"/>
+      <c r="E10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="21">
         <f>C10</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="9">
         <v>2025</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <v>2026</v>
       </c>
-      <c r="K10" s="11"/>
+      <c r="K10" s="10"/>
     </row>
     <row r="11" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="22">
         <v>2565</v>
       </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="22" t="s">
+      <c r="D11" s="7"/>
+      <c r="E11" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="23">
         <f>C11</f>
         <v>2565</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="15">
-        <v>44446</v>
-      </c>
-      <c r="J11" s="15">
-        <v>54571</v>
-      </c>
-      <c r="K11" s="11"/>
+      <c r="I11" s="14">
+        <v>45779</v>
+      </c>
+      <c r="J11" s="14">
+        <v>57013</v>
+      </c>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="24">
         <v>585</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="14" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="25">
         <f>C12/C$4</f>
         <v>18.870967741935484</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>0.2278045268415605</v>
-      </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="11"/>
+        <v>0.24539636077677529</v>
+      </c>
+      <c r="J12" s="57"/>
+      <c r="K12" s="10"/>
     </row>
     <row r="13" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="26">
         <v>1170</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="22" t="s">
+      <c r="D13" s="7"/>
+      <c r="E13" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="27">
         <f>C13/C$4</f>
         <v>37.741935483870968</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="14" spans="1:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="24">
         <v>8566</v>
       </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="14" t="s">
+      <c r="D14" s="7"/>
+      <c r="E14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="25">
         <f>C14/C$4</f>
         <v>276.32258064516128</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I14" s="10">
+      <c r="I14" s="9">
         <v>2025</v>
       </c>
-      <c r="J14" s="10">
+      <c r="J14" s="9">
         <v>2026</v>
       </c>
-      <c r="K14" s="33" t="s">
+      <c r="K14" s="28" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="H15" s="34" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="H15" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="35">
-        <v>960406</v>
-      </c>
-      <c r="J15" s="35">
-        <v>941690</v>
-      </c>
-      <c r="K15" s="36">
+      <c r="I15" s="30">
+        <v>1039498</v>
+      </c>
+      <c r="J15" s="30">
+        <v>990446</v>
+      </c>
+      <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-1.9487591706007668E-2</v>
+        <v>-4.718816197818565E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="37" t="s">
+      <c r="B16" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C16" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F16" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="I16" s="39">
-        <v>249962</v>
-      </c>
-      <c r="J16" s="39">
-        <v>241545</v>
-      </c>
-      <c r="K16" s="36">
+      <c r="I16" s="34">
+        <v>249963</v>
+      </c>
+      <c r="J16" s="34">
+        <v>249511</v>
+      </c>
+      <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-3.3673118313983674E-2</v>
+        <v>-1.8082676236083062E-3</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>1451612.9032258063</v>
-      </c>
-      <c r="D17" s="40">
-        <v>1328521</v>
-      </c>
-      <c r="E17" s="21">
+        <v>1548387.0967741935</v>
+      </c>
+      <c r="D17" s="35">
+        <v>1389956</v>
+      </c>
+      <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-123091.90322580631</v>
-      </c>
-      <c r="F17" s="26">
+        <v>-158431.09677419346</v>
+      </c>
+      <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-8.4796644444444361E-2</v>
-      </c>
-      <c r="H17" s="34" t="s">
+        <v>-0.10232008333333328</v>
+      </c>
+      <c r="H17" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="35">
-        <v>0</v>
-      </c>
-      <c r="J17" s="35">
-        <v>0</v>
-      </c>
-      <c r="K17" s="36" t="e">
+      <c r="I17" s="30">
+        <v>19117</v>
+      </c>
+      <c r="J17" s="30">
+        <v>8892</v>
+      </c>
+      <c r="K17" s="31">
         <f>J17/I17-1</f>
-        <v>#DIV/0!</v>
+        <v>-0.53486425694408113</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="37">
         <f>F9</f>
         <v>1.8</v>
       </c>
-      <c r="D18" s="43">
-        <v>1.65</v>
-      </c>
-      <c r="E18" s="42">
+      <c r="D18" s="38">
+        <v>1.64</v>
+      </c>
+      <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.15000000000000013</v>
-      </c>
-      <c r="F18" s="44">
+        <v>-0.16000000000000014</v>
+      </c>
+      <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-8.3333333333333412E-2</v>
-      </c>
-      <c r="H18" s="12" t="s">
+        <v>-8.8888888888888962E-2</v>
+      </c>
+      <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="I18" s="39">
-        <v>257743</v>
-      </c>
-      <c r="J18" s="39">
-        <v>135670</v>
-      </c>
-      <c r="K18" s="36">
+      <c r="I18" s="34">
+        <v>265503</v>
+      </c>
+      <c r="J18" s="34">
+        <v>149892</v>
+      </c>
+      <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.47362294999282228</v>
+        <v>-0.43544140744172377</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="21">
         <f>F10</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="D19" s="45">
-        <v>6.6799999999999998E-2</v>
-      </c>
-      <c r="E19" s="26">
+      <c r="D19" s="40">
+        <v>6.5500000000000003E-2</v>
+      </c>
+      <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-3.2000000000000084E-3</v>
-      </c>
-      <c r="F19" s="26">
+        <v>-4.500000000000004E-3</v>
+      </c>
+      <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-4.5714285714285832E-2</v>
-      </c>
-      <c r="H19" s="34" t="s">
+        <v>-6.4285714285714335E-2</v>
+      </c>
+      <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="46">
+      <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>1468111</v>
-      </c>
-      <c r="J19" s="46">
+        <v>1574081</v>
+      </c>
+      <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1318905</v>
-      </c>
-      <c r="K19" s="36">
+        <v>1398741</v>
+      </c>
+      <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.10163127992365695</v>
+        <v>-0.11139198046352128</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="C20" s="47">
+      <c r="C20" s="42">
         <f>F11</f>
         <v>2565</v>
       </c>
-      <c r="D20" s="48">
-        <v>3942</v>
-      </c>
-      <c r="E20" s="47">
+      <c r="D20" s="43">
+        <v>3971</v>
+      </c>
+      <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1377</v>
-      </c>
-      <c r="F20" s="44">
+        <v>1406</v>
+      </c>
+      <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.5368421052631579</v>
-      </c>
-      <c r="K20" s="49"/>
+        <v>0.54814814814814816</v>
+      </c>
+      <c r="K20" s="44"/>
     </row>
     <row r="21" spans="2:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>283.06451612903226</v>
-      </c>
-      <c r="D21" s="50">
-        <v>204</v>
-      </c>
-      <c r="E21" s="30">
+        <v>301.93548387096774</v>
+      </c>
+      <c r="D21" s="45">
+        <v>213</v>
+      </c>
+      <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-79.064516129032256</v>
-      </c>
-      <c r="F21" s="26">
+        <v>-88.935483870967744</v>
+      </c>
+      <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.27931623931623933</v>
-      </c>
-      <c r="H21" s="2" t="s">
+        <v>-0.29455128205128206</v>
+      </c>
+      <c r="H21" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
     </row>
     <row r="22" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="51">
+      <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>566.12903225806451</v>
-      </c>
-      <c r="D22" s="52">
-        <v>355</v>
-      </c>
-      <c r="E22" s="51">
+        <v>603.87096774193549</v>
+      </c>
+      <c r="D22" s="47">
+        <v>350</v>
+      </c>
+      <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-211.12903225806451</v>
-      </c>
-      <c r="F22" s="44">
+        <v>-253.87096774193549</v>
+      </c>
+      <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.3729344729344729</v>
+        <v>-0.42040598290598291</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>4144.8387096774195</v>
-      </c>
-      <c r="D23" s="50">
-        <v>3052</v>
-      </c>
-      <c r="E23" s="30">
+        <v>4421.1612903225805</v>
+      </c>
+      <c r="D23" s="45">
+        <v>3254</v>
+      </c>
+      <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1092.8387096774195</v>
-      </c>
-      <c r="F23" s="26">
+        <v>-1167.1612903225805</v>
+      </c>
+      <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.26366254183204924</v>
-      </c>
-      <c r="H23" s="53">
+        <v>-0.26399427971048328</v>
+      </c>
+      <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46311</v>
-      </c>
-      <c r="I23" s="10">
+        <v>46312</v>
+      </c>
+      <c r="I23" s="9">
         <v>2025</v>
       </c>
-      <c r="J23" s="10">
+      <c r="J23" s="9">
         <v>2026</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="H24" s="34" t="s">
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="H24" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="I24" s="54">
-        <v>1559</v>
-      </c>
-      <c r="J24" s="54">
-        <v>1484</v>
+      <c r="I24" s="49">
+        <v>1560</v>
+      </c>
+      <c r="J24" s="49">
+        <v>1498</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="56">
+      <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2745610.0666666664</v>
-      </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="55" t="s">
+        <v>2693039.75</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="36">
+      <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.91520335555555543</v>
-      </c>
-      <c r="H25" s="12" t="s">
+        <v>0.89767991666666669</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="I25" s="13">
-        <v>2498</v>
-      </c>
-      <c r="J25" s="57">
-        <v>3337</v>
+      <c r="I25" s="12">
+        <v>2500</v>
+      </c>
+      <c r="J25" s="52">
+        <v>3370</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="H26" s="34" t="s">
+      <c r="H26" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="I26" s="54">
+      <c r="I26" s="49">
         <v>289</v>
       </c>
-      <c r="J26" s="54">
-        <v>418</v>
+      <c r="J26" s="49">
+        <v>416</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4346</v>
-      </c>
-      <c r="J27" s="12">
+        <v>4349</v>
+      </c>
+      <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5239</v>
+        <v>5284</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="58"/>
-      <c r="C35" s="59"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="60"/>
+      <c r="B35" s="53"/>
+      <c r="C35" s="54"/>
+      <c r="E35" s="53"/>
+      <c r="F35" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76955B7E-4F13-4D22-9A39-F067014975A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75178DBE-61D8-47CF-9112-12516BB1F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1069,10 +1069,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>699546</v>
+        <v>727387</v>
       </c>
       <c r="J5" s="14">
-        <v>540298</v>
+        <v>596158</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.22764478676169975</v>
+        <v>-0.1804115278386883</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1132,10 +1132,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>809639</v>
+        <v>841237</v>
       </c>
       <c r="J8" s="14">
-        <v>792644</v>
+        <v>883029</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-2.0990836656830991E-2</v>
+        <v>4.9679222383228527E-2</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1209,10 +1209,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>45779</v>
+        <v>49141</v>
       </c>
       <c r="J11" s="14">
-        <v>57013</v>
+        <v>58885</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>0.24539636077677529</v>
+        <v>0.19828656315500304</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1299,14 +1299,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1039498</v>
+        <v>1083033</v>
       </c>
       <c r="J15" s="30">
-        <v>990446</v>
+        <v>1106612</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-4.718816197818565E-2</v>
+        <v>2.1771266434171377E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1329,14 +1329,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>249963</v>
+        <v>262504</v>
       </c>
       <c r="J16" s="34">
-        <v>249511</v>
+        <v>263007</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-1.8082676236083062E-3</v>
+        <v>1.9161612775424608E-3</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1345,31 +1345,27 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>1548387.0967741935</v>
+        <v>1645161.2903225806</v>
       </c>
       <c r="D17" s="35">
-        <v>1389956</v>
+        <v>1538072</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-158431.09677419346</v>
+        <v>-107089.29032258061</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.10232008333333328</v>
+        <v>-6.5093490196078407E-2</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="30">
-        <v>19117</v>
-      </c>
-      <c r="J17" s="30">
-        <v>8892</v>
-      </c>
-      <c r="K17" s="31">
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31" t="e">
         <f>J17/I17-1</f>
-        <v>-0.53486425694408113</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1381,28 +1377,28 @@
         <v>1.8</v>
       </c>
       <c r="D18" s="38">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.16000000000000014</v>
+        <v>-0.15000000000000013</v>
       </c>
       <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-8.8888888888888962E-2</v>
+        <v>-8.3333333333333412E-2</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>265503</v>
+        <v>272615</v>
       </c>
       <c r="J18" s="34">
-        <v>149892</v>
+        <v>168554</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.43544140744172377</v>
+        <v>-0.3817141389872164</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1414,30 +1410,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.5500000000000003E-2</v>
+        <v>6.5299999999999997E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-4.500000000000004E-3</v>
+        <v>-4.7000000000000097E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-6.4285714285714335E-2</v>
+        <v>-6.7142857142857282E-2</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>1574081</v>
+        <v>1618152</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1398741</v>
+        <v>1538173</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.11139198046352128</v>
+        <v>-4.9426135492833811E-2</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1449,15 +1445,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>3971</v>
+        <v>4026</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1406</v>
+        <v>1461</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.54814814814814816</v>
+        <v>0.56959064327485376</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1467,18 +1463,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>301.93548387096774</v>
+        <v>320.80645161290323</v>
       </c>
       <c r="D21" s="45">
-        <v>213</v>
+        <v>232</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-88.935483870967744</v>
+        <v>-88.806451612903231</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.29455128205128206</v>
+        <v>-0.27682252388134743</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1493,18 +1489,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>603.87096774193549</v>
+        <v>641.61290322580646</v>
       </c>
       <c r="D22" s="47">
-        <v>350</v>
+        <v>382</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-253.87096774193549</v>
+        <v>-259.61290322580646</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.42040598290598291</v>
+        <v>-0.40462543991955757</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1513,22 +1509,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>4421.1612903225805</v>
+        <v>4697.4838709677415</v>
       </c>
       <c r="D23" s="45">
-        <v>3254</v>
+        <v>3553</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1167.1612903225805</v>
+        <v>-1144.4838709677415</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.26399427971048328</v>
+        <v>-0.24363763717020773</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1547,10 +1543,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1560</v>
+        <v>1682</v>
       </c>
       <c r="J24" s="49">
-        <v>1498</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1559,7 +1555,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2693039.75</v>
+        <v>2804719.5294117648</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1567,16 +1563,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.89767991666666669</v>
+        <v>0.93490650980392165</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2500</v>
+        <v>2638</v>
       </c>
       <c r="J25" s="52">
-        <v>3370</v>
+        <v>3332</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1584,10 +1580,10 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="J26" s="49">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1596,11 +1592,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4349</v>
+        <v>4624</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5284</v>
+        <v>5233</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75178DBE-61D8-47CF-9112-12516BB1F1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16316DDB-25F3-48A5-BE4E-897E51D6FB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1060,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1069,10 +1069,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>727387</v>
+        <v>765071</v>
       </c>
       <c r="J5" s="14">
-        <v>596158</v>
+        <v>654992</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.1804115278386883</v>
+        <v>-0.14388076400752348</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1132,10 +1132,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>841237</v>
+        <v>911784</v>
       </c>
       <c r="J8" s="14">
-        <v>883029</v>
+        <v>967652</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>4.9679222383228527E-2</v>
+        <v>6.1273284023409147E-2</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1209,10 +1209,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>49141</v>
+        <v>54264</v>
       </c>
       <c r="J11" s="14">
-        <v>58885</v>
+        <v>61178</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1236,7 +1236,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>0.19828656315500304</v>
+        <v>0.1274141235441546</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1299,14 +1299,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1083033</v>
+        <v>1165723</v>
       </c>
       <c r="J15" s="30">
-        <v>1106612</v>
+        <v>1230525</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>2.1771266434171377E-2</v>
+        <v>5.5589535421365133E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1329,14 +1329,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>262504</v>
+        <v>286557</v>
       </c>
       <c r="J16" s="34">
-        <v>263007</v>
+        <v>265974</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>1.9161612775424608E-3</v>
+        <v>-7.1828641422125417E-2</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1345,18 +1345,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>1645161.2903225806</v>
+        <v>1741935.4838709678</v>
       </c>
       <c r="D17" s="35">
-        <v>1538072</v>
+        <v>1683822</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-107089.29032258061</v>
+        <v>-58113.483870967757</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-6.5093490196078407E-2</v>
+        <v>-3.3361444444444451E-2</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1377,28 +1377,28 @@
         <v>1.8</v>
       </c>
       <c r="D18" s="38">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.15000000000000013</v>
+        <v>-0.14000000000000012</v>
       </c>
       <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-8.3333333333333412E-2</v>
+        <v>-7.7777777777777848E-2</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>272615</v>
+        <v>279221</v>
       </c>
       <c r="J18" s="34">
-        <v>168554</v>
+        <v>187409</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.3817141389872164</v>
+        <v>-0.32881480977433641</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1410,30 +1410,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.5299999999999997E-2</v>
+        <v>6.2199999999999998E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-4.7000000000000097E-3</v>
+        <v>-7.8000000000000083E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-6.7142857142857282E-2</v>
+        <v>-0.11142857142857154</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>1618152</v>
+        <v>1731501</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1538173</v>
+        <v>1683908</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-4.9426135492833811E-2</v>
+        <v>-2.7486556461705725E-2</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1445,15 +1445,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4026</v>
+        <v>4028</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.56959064327485376</v>
+        <v>0.57037037037037042</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1463,18 +1463,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>320.80645161290323</v>
+        <v>339.67741935483872</v>
       </c>
       <c r="D21" s="45">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-88.806451612903231</v>
+        <v>-87.677419354838719</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.27682252388134743</v>
+        <v>-0.25811965811965815</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1489,18 +1489,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>641.61290322580646</v>
+        <v>679.35483870967744</v>
       </c>
       <c r="D22" s="47">
-        <v>382</v>
+        <v>418</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-259.61290322580646</v>
+        <v>-261.35483870967744</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.40462543991955757</v>
+        <v>-0.38471035137701803</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1509,22 +1509,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>4697.4838709677415</v>
+        <v>4973.8064516129034</v>
       </c>
       <c r="D23" s="45">
-        <v>3553</v>
+        <v>4053</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1144.4838709677415</v>
+        <v>-920.8064516129034</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.24363763717020773</v>
+        <v>-0.1851311386100086</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1543,10 +1543,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1682</v>
+        <v>1656</v>
       </c>
       <c r="J24" s="49">
-        <v>1486</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2804719.5294117648</v>
+        <v>2899915.666666667</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1563,16 +1563,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.93490650980392165</v>
+        <v>0.96663855555555567</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2638</v>
+        <v>2603</v>
       </c>
       <c r="J25" s="52">
-        <v>3332</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1580,10 +1580,10 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="J26" s="49">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1592,11 +1592,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4624</v>
+        <v>4557</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5233</v>
+        <v>5198</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16316DDB-25F3-48A5-BE4E-897E51D6FB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2D9412-7BA3-492F-B64D-B5A51BEE5215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -559,6 +559,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1000,41 +1003,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K35"/>
+  <dimension ref="A2:V33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="4" customWidth="1"/>
     <col min="2" max="2" width="31.6640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="36.5546875" style="4" customWidth="1"/>
-    <col min="4" max="6" width="31.6640625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="33.44140625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="23.5546875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="20.5546875" style="4" customWidth="1"/>
     <col min="7" max="7" width="3.33203125" customWidth="1"/>
     <col min="8" max="10" width="26" customWidth="1"/>
     <col min="11" max="11" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:11" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
       <c r="F2" s="1"/>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-    </row>
-    <row r="3" spans="1:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="I2" s="59"/>
+      <c r="J2" s="59"/>
+      <c r="K2" s="59"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+    </row>
+    <row r="3" spans="1:22" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-    </row>
-    <row r="4" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="M3" s="56"/>
+      <c r="N3" s="56"/>
+      <c r="O3" s="56"/>
+      <c r="P3" s="56"/>
+      <c r="Q3" s="56"/>
+      <c r="R3" s="56"/>
+      <c r="S3" s="56"/>
+      <c r="T3" s="56"/>
+      <c r="U3" s="56"/>
+      <c r="V3" s="56"/>
+    </row>
+    <row r="4" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1054,13 +1079,23 @@
         <v>2026</v>
       </c>
       <c r="K4" s="10"/>
-    </row>
-    <row r="5" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
+      <c r="U4" s="56"/>
+      <c r="V4" s="56"/>
+    </row>
+    <row r="5" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1069,14 +1104,24 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>765071</v>
+        <v>870953</v>
       </c>
       <c r="J5" s="14">
-        <v>654992</v>
+        <v>668356.39</v>
       </c>
       <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+    </row>
+    <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1085,23 +1130,33 @@
       <c r="H6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="57">
         <f>J5/I5-1</f>
-        <v>-0.14388076400752348</v>
-      </c>
-      <c r="J6" s="57"/>
+        <v>-0.23261485981447905</v>
+      </c>
+      <c r="J6" s="58"/>
       <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B7" s="59" t="s">
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="56"/>
+      <c r="U6" s="56"/>
+      <c r="V6" s="56"/>
+    </row>
+    <row r="7" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="B7" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="60"/>
+      <c r="C7" s="61"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="60"/>
+      <c r="F7" s="61"/>
       <c r="H7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1112,8 +1167,18 @@
         <v>2026</v>
       </c>
       <c r="K7" s="10"/>
-    </row>
-    <row r="8" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="56"/>
+      <c r="U7" s="56"/>
+      <c r="V7" s="56"/>
+    </row>
+    <row r="8" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B8" s="13" t="s">
         <v>5</v>
       </c>
@@ -1132,14 +1197,24 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>911784</v>
+        <v>1021558</v>
       </c>
       <c r="J8" s="14">
-        <v>967652</v>
+        <v>981808.11</v>
       </c>
       <c r="K8" s="10"/>
-    </row>
-    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="M8" s="56"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="56"/>
+      <c r="V8" s="56"/>
+    </row>
+    <row r="9" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
@@ -1157,14 +1232,24 @@
       <c r="H9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="56">
+      <c r="I9" s="57">
         <f>J8/I8-1</f>
-        <v>6.1273284023409147E-2</v>
-      </c>
-      <c r="J9" s="57"/>
+        <v>-3.891104567728898E-2</v>
+      </c>
+      <c r="J9" s="58"/>
       <c r="K9" s="10"/>
-    </row>
-    <row r="10" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="M9" s="56"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="56"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="56"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="56"/>
+      <c r="U9" s="56"/>
+      <c r="V9" s="56"/>
+    </row>
+    <row r="10" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
@@ -1189,8 +1274,18 @@
         <v>2026</v>
       </c>
       <c r="K10" s="10"/>
-    </row>
-    <row r="11" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="56"/>
+    </row>
+    <row r="11" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
         <v>13</v>
       </c>
@@ -1209,14 +1304,24 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>54264</v>
+        <v>59646</v>
       </c>
       <c r="J11" s="14">
-        <v>61178</v>
+        <v>60677.96</v>
       </c>
       <c r="K11" s="10"/>
-    </row>
-    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="56"/>
+      <c r="V11" s="56"/>
+    </row>
+    <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="13" t="s">
         <v>14</v>
       </c>
@@ -1234,14 +1339,24 @@
       <c r="H12" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="56">
+      <c r="I12" s="57">
         <f>J11/I11-1</f>
-        <v>0.1274141235441546</v>
-      </c>
-      <c r="J12" s="57"/>
+        <v>1.7301411662139943E-2</v>
+      </c>
+      <c r="J12" s="58"/>
       <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="56"/>
+    </row>
+    <row r="13" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
         <v>15</v>
       </c>
@@ -1260,8 +1375,18 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-    </row>
-    <row r="14" spans="1:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="56"/>
+      <c r="V13" s="56"/>
+    </row>
+    <row r="14" spans="1:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>16</v>
       </c>
@@ -1288,8 +1413,18 @@
       <c r="K14" s="28" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="56"/>
+      <c r="V14" s="56"/>
+    </row>
+    <row r="15" spans="1:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1299,17 +1434,27 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1165723</v>
+        <v>1314835</v>
       </c>
       <c r="J15" s="30">
-        <v>1230525</v>
+        <v>1244681</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>5.5589535421365133E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-5.3355744256883941E-2</v>
+      </c>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="56"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="56"/>
+      <c r="U15" s="56"/>
+      <c r="V15" s="56"/>
+    </row>
+    <row r="16" spans="1:22" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="32" t="s">
         <v>19</v>
       </c>
@@ -1329,46 +1474,70 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>286557</v>
+        <v>301788</v>
       </c>
       <c r="J16" s="34">
-        <v>265974</v>
+        <v>279336</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-7.1828641422125417E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-7.4396596286134598E-2</v>
+      </c>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="56"/>
+      <c r="U16" s="56"/>
+      <c r="V16" s="56"/>
+    </row>
+    <row r="17" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>1741935.4838709678</v>
+        <v>1838709.6774193547</v>
       </c>
       <c r="D17" s="35">
-        <v>1683822</v>
+        <v>1711340</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-58113.483870967757</v>
+        <v>-127369.67741935467</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-3.3361444444444451E-2</v>
+        <v>-6.9271228070175356E-2</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="31" t="e">
+      <c r="I17" s="30">
+        <v>22753</v>
+      </c>
+      <c r="J17" s="30">
+        <v>8892</v>
+      </c>
+      <c r="K17" s="31">
         <f>J17/I17-1</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.60919439194831448</v>
+      </c>
+      <c r="M17" s="56"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="56"/>
+      <c r="P17" s="56"/>
+      <c r="Q17" s="56"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="56"/>
+      <c r="U17" s="56"/>
+      <c r="V17" s="56"/>
+    </row>
+    <row r="18" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
         <v>10</v>
       </c>
@@ -1377,31 +1546,41 @@
         <v>1.8</v>
       </c>
       <c r="D18" s="38">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.14000000000000012</v>
+        <v>-0.16000000000000014</v>
       </c>
       <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-7.7777777777777848E-2</v>
+        <v>-8.8888888888888962E-2</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>279221</v>
+        <v>335354</v>
       </c>
       <c r="J18" s="34">
-        <v>187409</v>
+        <v>186826</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.32881480977433641</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.44289914538070219</v>
+      </c>
+      <c r="M18" s="56"/>
+      <c r="N18" s="56"/>
+      <c r="O18" s="56"/>
+      <c r="P18" s="56"/>
+      <c r="Q18" s="56"/>
+      <c r="R18" s="56"/>
+      <c r="S18" s="56"/>
+      <c r="T18" s="56"/>
+      <c r="U18" s="56"/>
+      <c r="V18" s="56"/>
+    </row>
+    <row r="19" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>11</v>
       </c>
@@ -1410,33 +1589,43 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.2199999999999998E-2</v>
+        <v>6.1600000000000002E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-7.8000000000000083E-3</v>
+        <v>-8.4000000000000047E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.11142857142857154</v>
+        <v>-0.12000000000000005</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>1731501</v>
+        <v>1974730</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1683908</v>
+        <v>1719735</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-2.7486556461705725E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.12912904548976312</v>
+      </c>
+      <c r="M19" s="56"/>
+      <c r="N19" s="56"/>
+      <c r="O19" s="56"/>
+      <c r="P19" s="56"/>
+      <c r="Q19" s="56"/>
+      <c r="R19" s="56"/>
+      <c r="S19" s="56"/>
+      <c r="T19" s="56"/>
+      <c r="U19" s="56"/>
+      <c r="V19" s="56"/>
+    </row>
+    <row r="20" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
@@ -1445,86 +1634,116 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4028</v>
+        <v>4065</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1463</v>
+        <v>1500</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.57037037037037042</v>
+        <v>0.58479532163742687</v>
       </c>
       <c r="K20" s="44"/>
-    </row>
-    <row r="21" spans="2:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="M20" s="56"/>
+      <c r="N20" s="56"/>
+      <c r="O20" s="56"/>
+      <c r="P20" s="56"/>
+      <c r="Q20" s="56"/>
+      <c r="R20" s="56"/>
+      <c r="S20" s="56"/>
+      <c r="T20" s="56"/>
+      <c r="U20" s="56"/>
+      <c r="V20" s="56"/>
+    </row>
+    <row r="21" spans="2:22" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>339.67741935483872</v>
+        <v>358.54838709677421</v>
       </c>
       <c r="D21" s="45">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-87.677419354838719</v>
+        <v>-102.54838709677421</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.25811965811965815</v>
-      </c>
-      <c r="H21" s="58" t="s">
+        <v>-0.28600989653621234</v>
+      </c>
+      <c r="H21" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-    </row>
-    <row r="22" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="I21" s="59"/>
+      <c r="J21" s="59"/>
+      <c r="K21" s="59"/>
+      <c r="M21" s="56"/>
+      <c r="N21" s="56"/>
+      <c r="O21" s="56"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="56"/>
+      <c r="R21" s="56"/>
+      <c r="S21" s="56"/>
+      <c r="T21" s="56"/>
+      <c r="U21" s="56"/>
+      <c r="V21" s="56"/>
+    </row>
+    <row r="22" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>679.35483870967744</v>
+        <v>717.09677419354841</v>
       </c>
       <c r="D22" s="47">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-261.35483870967744</v>
+        <v>-296.09677419354841</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.38471035137701803</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.41291048133153396</v>
+      </c>
+      <c r="M22" s="56"/>
+      <c r="N22" s="56"/>
+      <c r="O22" s="56"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="56"/>
+      <c r="R22" s="56"/>
+      <c r="S22" s="56"/>
+      <c r="T22" s="56"/>
+      <c r="U22" s="56"/>
+      <c r="V22" s="56"/>
+    </row>
+    <row r="23" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>4973.8064516129034</v>
+        <v>5250.1290322580644</v>
       </c>
       <c r="D23" s="45">
-        <v>4053</v>
+        <v>4159</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-920.8064516129034</v>
+        <v>-1091.1290322580644</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.1851311386100086</v>
+        <v>-0.20782899345023775</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1532,8 +1751,18 @@
       <c r="J23" s="9">
         <v>2026</v>
       </c>
-    </row>
-    <row r="24" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="M23" s="56"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+      <c r="P23" s="56"/>
+      <c r="Q23" s="56"/>
+      <c r="R23" s="56"/>
+      <c r="S23" s="56"/>
+      <c r="T23" s="56"/>
+      <c r="U23" s="56"/>
+      <c r="V23" s="56"/>
+    </row>
+    <row r="24" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -1543,19 +1772,29 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="J24" s="49">
-        <v>1474</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>1476</v>
+      </c>
+      <c r="M24" s="56"/>
+      <c r="N24" s="56"/>
+      <c r="O24" s="56"/>
+      <c r="P24" s="56"/>
+      <c r="Q24" s="56"/>
+      <c r="R24" s="56"/>
+      <c r="S24" s="56"/>
+      <c r="T24" s="56"/>
+      <c r="U24" s="56"/>
+      <c r="V24" s="56"/>
+    </row>
+    <row r="25" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B25" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2899915.666666667</v>
+        <v>2792186.3157894737</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1563,19 +1802,29 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.96663855555555567</v>
+        <v>0.93072877192982462</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2603</v>
+        <v>2605</v>
       </c>
       <c r="J25" s="52">
-        <v>3311</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>3321</v>
+      </c>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
+      <c r="P25" s="56"/>
+      <c r="Q25" s="56"/>
+      <c r="R25" s="56"/>
+      <c r="S25" s="56"/>
+      <c r="T25" s="56"/>
+      <c r="U25" s="56"/>
+      <c r="V25" s="56"/>
+    </row>
+    <row r="26" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="H26" s="29" t="s">
         <v>33</v>
       </c>
@@ -1583,30 +1832,111 @@
         <v>298</v>
       </c>
       <c r="J26" s="49">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>412</v>
+      </c>
+      <c r="M26" s="56"/>
+      <c r="N26" s="56"/>
+      <c r="O26" s="56"/>
+      <c r="P26" s="56"/>
+      <c r="Q26" s="56"/>
+      <c r="R26" s="56"/>
+      <c r="S26" s="56"/>
+      <c r="T26" s="56"/>
+      <c r="U26" s="56"/>
+      <c r="V26" s="56"/>
+    </row>
+    <row r="27" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="H27" s="11" t="s">
         <v>27</v>
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4557</v>
+        <v>4560</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5198</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B35" s="53"/>
-      <c r="C35" s="54"/>
-      <c r="E35" s="53"/>
-      <c r="F35" s="55"/>
+        <v>5209</v>
+      </c>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="56"/>
+      <c r="R27" s="56"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="56"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="56"/>
+    </row>
+    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="M28" s="56"/>
+      <c r="N28" s="56"/>
+      <c r="O28" s="56"/>
+      <c r="P28" s="56"/>
+      <c r="Q28" s="56"/>
+      <c r="R28" s="56"/>
+      <c r="S28" s="56"/>
+      <c r="T28" s="56"/>
+      <c r="U28" s="56"/>
+      <c r="V28" s="56"/>
+    </row>
+    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="M29" s="56"/>
+      <c r="N29" s="56"/>
+      <c r="O29" s="56"/>
+      <c r="P29" s="56"/>
+      <c r="Q29" s="56"/>
+      <c r="R29" s="56"/>
+      <c r="S29" s="56"/>
+      <c r="T29" s="56"/>
+      <c r="U29" s="56"/>
+      <c r="V29" s="56"/>
+    </row>
+    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="56"/>
+      <c r="V30" s="56"/>
+    </row>
+    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="M31" s="56"/>
+      <c r="N31" s="56"/>
+      <c r="O31" s="56"/>
+      <c r="P31" s="56"/>
+      <c r="Q31" s="56"/>
+      <c r="R31" s="56"/>
+      <c r="S31" s="56"/>
+      <c r="T31" s="56"/>
+      <c r="U31" s="56"/>
+      <c r="V31" s="56"/>
+    </row>
+    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
+      <c r="M32" s="56"/>
+      <c r="N32" s="56"/>
+      <c r="O32" s="56"/>
+      <c r="P32" s="56"/>
+      <c r="Q32" s="56"/>
+      <c r="R32" s="56"/>
+      <c r="S32" s="56"/>
+      <c r="T32" s="56"/>
+      <c r="U32" s="56"/>
+      <c r="V32" s="56"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B33" s="53"/>
+      <c r="C33" s="54"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="M2:V32"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="B2:E2"/>

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B2D9412-7BA3-492F-B64D-B5A51BEE5215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DBF2E4-6440-41F1-A05C-ED12F5230036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1095,7 +1095,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1104,10 +1104,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>870953</v>
+        <v>895373.1</v>
       </c>
       <c r="J5" s="14">
-        <v>668356.39</v>
+        <v>683401</v>
       </c>
       <c r="K5" s="10"/>
       <c r="M5" s="56"/>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="I6" s="57">
         <f>J5/I5-1</f>
-        <v>-0.23261485981447905</v>
+        <v>-0.23674164434915457</v>
       </c>
       <c r="J6" s="58"/>
       <c r="K6" s="10"/>
@@ -1197,10 +1197,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>1021558</v>
+        <v>1041762.31</v>
       </c>
       <c r="J8" s="14">
-        <v>981808.11</v>
+        <v>1016116</v>
       </c>
       <c r="K8" s="10"/>
       <c r="M8" s="56"/>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="I9" s="57">
         <f>J8/I8-1</f>
-        <v>-3.891104567728898E-2</v>
+        <v>-2.4618197216215387E-2</v>
       </c>
       <c r="J9" s="58"/>
       <c r="K9" s="10"/>
@@ -1304,10 +1304,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>59646</v>
+        <v>59466.12</v>
       </c>
       <c r="J11" s="14">
-        <v>60677.96</v>
+        <v>61178</v>
       </c>
       <c r="K11" s="10"/>
       <c r="M11" s="56"/>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="I12" s="57">
         <f>J11/I11-1</f>
-        <v>1.7301411662139943E-2</v>
+        <v>2.8787484369250826E-2</v>
       </c>
       <c r="J12" s="58"/>
       <c r="K12" s="10"/>
@@ -1434,14 +1434,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1314835</v>
+        <v>1337584.22</v>
       </c>
       <c r="J15" s="30">
-        <v>1244681</v>
+        <v>1282765.26</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-5.3355744256883941E-2</v>
+        <v>-4.0983557655905889E-2</v>
       </c>
       <c r="M15" s="56"/>
       <c r="N15" s="56"/>
@@ -1474,14 +1474,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>301788</v>
+        <v>311149.17</v>
       </c>
       <c r="J16" s="34">
-        <v>279336</v>
+        <v>290606.49</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-7.4396596286134598E-2</v>
+        <v>-6.6021966248536068E-2</v>
       </c>
       <c r="M16" s="56"/>
       <c r="N16" s="56"/>
@@ -1500,31 +1500,27 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>1838709.6774193547</v>
+        <v>1935483.8709677418</v>
       </c>
       <c r="D17" s="35">
-        <v>1711340</v>
+        <v>1760695</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-127369.67741935467</v>
+        <v>-174788.87096774182</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-6.9271228070175356E-2</v>
+        <v>-9.0307583333333274E-2</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I17" s="30">
-        <v>22753</v>
-      </c>
-      <c r="J17" s="30">
-        <v>8892</v>
-      </c>
-      <c r="K17" s="31">
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31" t="e">
         <f>J17/I17-1</f>
-        <v>-0.60919439194831448</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M17" s="56"/>
       <c r="N17" s="56"/>
@@ -1560,14 +1556,14 @@
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>335354</v>
+        <v>347868.14</v>
       </c>
       <c r="J18" s="34">
-        <v>186826</v>
+        <v>186825.92</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.44289914538070219</v>
+        <v>-0.46294041184685664</v>
       </c>
       <c r="M18" s="56"/>
       <c r="N18" s="56"/>
@@ -1589,30 +1585,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.1600000000000002E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-8.4000000000000047E-3</v>
+        <v>-8.0000000000000071E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.12000000000000005</v>
+        <v>-0.11428571428571438</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>1974730</v>
+        <v>1996601.5299999998</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1719735</v>
+        <v>1760197.67</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.12912904548976312</v>
+        <v>-0.11840312473365677</v>
       </c>
       <c r="M19" s="56"/>
       <c r="N19" s="56"/>
@@ -1634,15 +1630,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4065</v>
+        <v>4076</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1500</v>
+        <v>1511</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.58479532163742687</v>
+        <v>0.58908382066276799</v>
       </c>
       <c r="K20" s="44"/>
       <c r="M20" s="56"/>
@@ -1662,18 +1658,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>358.54838709677421</v>
+        <v>377.41935483870969</v>
       </c>
       <c r="D21" s="45">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-102.54838709677421</v>
+        <v>-113.41935483870969</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.28600989653621234</v>
+        <v>-0.30051282051282052</v>
       </c>
       <c r="H21" s="59" t="s">
         <v>28</v>
@@ -1698,18 +1694,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>717.09677419354841</v>
+        <v>754.83870967741939</v>
       </c>
       <c r="D22" s="47">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-296.09677419354841</v>
+        <v>-322.83870967741939</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.41291048133153396</v>
+        <v>-0.4276923076923077</v>
       </c>
       <c r="M22" s="56"/>
       <c r="N22" s="56"/>
@@ -1728,22 +1724,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>5250.1290322580644</v>
+        <v>5526.4516129032254</v>
       </c>
       <c r="D23" s="45">
-        <v>4159</v>
+        <v>4257</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1091.1290322580644</v>
+        <v>-1269.4516129032254</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.20782899345023775</v>
+        <v>-0.22970464627597473</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1772,10 +1768,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="J24" s="49">
-        <v>1476</v>
+        <v>1469</v>
       </c>
       <c r="M24" s="56"/>
       <c r="N24" s="56"/>
@@ -1794,7 +1790,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2792186.3157894737</v>
+        <v>2729077.25</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1802,16 +1798,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.93072877192982462</v>
+        <v>0.90969241666666667</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2605</v>
+        <v>2597</v>
       </c>
       <c r="J25" s="52">
-        <v>3321</v>
+        <v>3312</v>
       </c>
       <c r="M25" s="56"/>
       <c r="N25" s="56"/>
@@ -1829,7 +1825,7 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J26" s="49">
         <v>412</v>
@@ -1851,11 +1847,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4560</v>
+        <v>4549</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5209</v>
+        <v>5193</v>
       </c>
       <c r="M27" s="56"/>
       <c r="N27" s="56"/>

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22DBF2E4-6440-41F1-A05C-ED12F5230036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F771AF7-B270-478A-B9A5-B8FB922B1EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -559,9 +559,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -1003,7 +1000,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:V33"/>
+  <dimension ref="A2:K33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="4" customWidth="1"/>
@@ -1017,49 +1014,29 @@
     <col min="11" max="11" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:22" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" s="3" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
       <c r="F2" s="1"/>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-    </row>
-    <row r="3" spans="1:22" ht="20.399999999999999" x14ac:dyDescent="0.3">
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+    </row>
+    <row r="3" spans="1:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
-      <c r="M3" s="56"/>
-      <c r="N3" s="56"/>
-      <c r="O3" s="56"/>
-      <c r="P3" s="56"/>
-      <c r="Q3" s="56"/>
-      <c r="R3" s="56"/>
-      <c r="S3" s="56"/>
-      <c r="T3" s="56"/>
-      <c r="U3" s="56"/>
-      <c r="V3" s="56"/>
-    </row>
-    <row r="4" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1079,23 +1056,13 @@
         <v>2026</v>
       </c>
       <c r="K4" s="10"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-      <c r="U4" s="56"/>
-      <c r="V4" s="56"/>
-    </row>
-    <row r="5" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B5" s="11" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1104,24 +1071,14 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>895373.1</v>
+        <v>966530</v>
       </c>
       <c r="J5" s="14">
-        <v>683401</v>
+        <v>689858</v>
       </c>
       <c r="K5" s="10"/>
-      <c r="M5" s="56"/>
-      <c r="N5" s="56"/>
-      <c r="O5" s="56"/>
-      <c r="P5" s="56"/>
-      <c r="Q5" s="56"/>
-      <c r="R5" s="56"/>
-      <c r="S5" s="56"/>
-      <c r="T5" s="56"/>
-      <c r="U5" s="56"/>
-      <c r="V5" s="56"/>
-    </row>
-    <row r="6" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1130,33 +1087,23 @@
       <c r="H6" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.23674164434915457</v>
-      </c>
-      <c r="J6" s="58"/>
+        <v>-0.28625288402843163</v>
+      </c>
+      <c r="J6" s="57"/>
       <c r="K6" s="10"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="56"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="56"/>
-      <c r="U6" s="56"/>
-      <c r="V6" s="56"/>
-    </row>
-    <row r="7" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
-      <c r="B7" s="60" t="s">
+    </row>
+    <row r="7" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
+      <c r="B7" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="61"/>
+      <c r="C7" s="60"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="60" t="s">
+      <c r="E7" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="61"/>
+      <c r="F7" s="60"/>
       <c r="H7" s="8" t="s">
         <v>9</v>
       </c>
@@ -1167,18 +1114,8 @@
         <v>2026</v>
       </c>
       <c r="K7" s="10"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="56"/>
-      <c r="O7" s="56"/>
-      <c r="P7" s="56"/>
-      <c r="Q7" s="56"/>
-      <c r="R7" s="56"/>
-      <c r="S7" s="56"/>
-      <c r="T7" s="56"/>
-      <c r="U7" s="56"/>
-      <c r="V7" s="56"/>
-    </row>
-    <row r="8" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B8" s="13" t="s">
         <v>5</v>
       </c>
@@ -1197,24 +1134,14 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>1041762.31</v>
+        <v>1139590</v>
       </c>
       <c r="J8" s="14">
-        <v>1016116</v>
+        <v>1022206</v>
       </c>
       <c r="K8" s="10"/>
-      <c r="M8" s="56"/>
-      <c r="N8" s="56"/>
-      <c r="O8" s="56"/>
-      <c r="P8" s="56"/>
-      <c r="Q8" s="56"/>
-      <c r="R8" s="56"/>
-      <c r="S8" s="56"/>
-      <c r="T8" s="56"/>
-      <c r="U8" s="56"/>
-      <c r="V8" s="56"/>
-    </row>
-    <row r="9" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="9" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="17" t="s">
         <v>10</v>
       </c>
@@ -1232,24 +1159,14 @@
       <c r="H9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I9" s="57">
+      <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-2.4618197216215387E-2</v>
-      </c>
-      <c r="J9" s="58"/>
+        <v>-0.1030054668784387</v>
+      </c>
+      <c r="J9" s="57"/>
       <c r="K9" s="10"/>
-      <c r="M9" s="56"/>
-      <c r="N9" s="56"/>
-      <c r="O9" s="56"/>
-      <c r="P9" s="56"/>
-      <c r="Q9" s="56"/>
-      <c r="R9" s="56"/>
-      <c r="S9" s="56"/>
-      <c r="T9" s="56"/>
-      <c r="U9" s="56"/>
-      <c r="V9" s="56"/>
-    </row>
-    <row r="10" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
@@ -1274,18 +1191,8 @@
         <v>2026</v>
       </c>
       <c r="K10" s="10"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-    </row>
-    <row r="11" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
         <v>13</v>
       </c>
@@ -1304,24 +1211,14 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>59466.12</v>
+        <v>61359</v>
       </c>
       <c r="J11" s="14">
-        <v>61178</v>
+        <v>61677</v>
       </c>
       <c r="K11" s="10"/>
-      <c r="M11" s="56"/>
-      <c r="N11" s="56"/>
-      <c r="O11" s="56"/>
-      <c r="P11" s="56"/>
-      <c r="Q11" s="56"/>
-      <c r="R11" s="56"/>
-      <c r="S11" s="56"/>
-      <c r="T11" s="56"/>
-      <c r="U11" s="56"/>
-      <c r="V11" s="56"/>
-    </row>
-    <row r="12" spans="1:22" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="12" spans="1:11" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="13" t="s">
         <v>14</v>
       </c>
@@ -1339,24 +1236,14 @@
       <c r="H12" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I12" s="57">
+      <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>2.8787484369250826E-2</v>
-      </c>
-      <c r="J12" s="58"/>
+        <v>5.1826137974868569E-3</v>
+      </c>
+      <c r="J12" s="57"/>
       <c r="K12" s="10"/>
-      <c r="M12" s="56"/>
-      <c r="N12" s="56"/>
-      <c r="O12" s="56"/>
-      <c r="P12" s="56"/>
-      <c r="Q12" s="56"/>
-      <c r="R12" s="56"/>
-      <c r="S12" s="56"/>
-      <c r="T12" s="56"/>
-      <c r="U12" s="56"/>
-      <c r="V12" s="56"/>
-    </row>
-    <row r="13" spans="1:22" ht="19.8" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:11" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B13" s="17" t="s">
         <v>15</v>
       </c>
@@ -1375,18 +1262,8 @@
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="56"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-    </row>
-    <row r="14" spans="1:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B14" s="13" t="s">
         <v>16</v>
       </c>
@@ -1413,18 +1290,8 @@
       <c r="K14" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="M14" s="56"/>
-      <c r="N14" s="56"/>
-      <c r="O14" s="56"/>
-      <c r="P14" s="56"/>
-      <c r="Q14" s="56"/>
-      <c r="R14" s="56"/>
-      <c r="S14" s="56"/>
-      <c r="T14" s="56"/>
-      <c r="U14" s="56"/>
-      <c r="V14" s="56"/>
-    </row>
-    <row r="15" spans="1:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1434,27 +1301,17 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1337584.22</v>
+        <v>1457774</v>
       </c>
       <c r="J15" s="30">
-        <v>1282765.26</v>
+        <v>1295218</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-4.0983557655905889E-2</v>
-      </c>
-      <c r="M15" s="56"/>
-      <c r="N15" s="56"/>
-      <c r="O15" s="56"/>
-      <c r="P15" s="56"/>
-      <c r="Q15" s="56"/>
-      <c r="R15" s="56"/>
-      <c r="S15" s="56"/>
-      <c r="T15" s="56"/>
-      <c r="U15" s="56"/>
-      <c r="V15" s="56"/>
-    </row>
-    <row r="16" spans="1:22" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>-0.11150974019292426</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="32" t="s">
         <v>19</v>
       </c>
@@ -1474,44 +1331,34 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>311149.17</v>
+        <v>348139</v>
       </c>
       <c r="J16" s="34">
-        <v>290606.49</v>
+        <v>285607</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-6.6021966248536068E-2</v>
-      </c>
-      <c r="M16" s="56"/>
-      <c r="N16" s="56"/>
-      <c r="O16" s="56"/>
-      <c r="P16" s="56"/>
-      <c r="Q16" s="56"/>
-      <c r="R16" s="56"/>
-      <c r="S16" s="56"/>
-      <c r="T16" s="56"/>
-      <c r="U16" s="56"/>
-      <c r="V16" s="56"/>
-    </row>
-    <row r="17" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.17961791123660376</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B17" s="13" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>1935483.8709677418</v>
+        <v>2129032.2580645159</v>
       </c>
       <c r="D17" s="35">
-        <v>1760695</v>
+        <v>1773239</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-174788.87096774182</v>
+        <v>-355793.25806451589</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-9.0307583333333274E-2</v>
+        <v>-0.16711501515151506</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1522,18 +1369,8 @@
         <f>J17/I17-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M17" s="56"/>
-      <c r="N17" s="56"/>
-      <c r="O17" s="56"/>
-      <c r="P17" s="56"/>
-      <c r="Q17" s="56"/>
-      <c r="R17" s="56"/>
-      <c r="S17" s="56"/>
-      <c r="T17" s="56"/>
-      <c r="U17" s="56"/>
-      <c r="V17" s="56"/>
-    </row>
-    <row r="18" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B18" s="36" t="s">
         <v>10</v>
       </c>
@@ -1556,27 +1393,17 @@
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>347868.14</v>
+        <v>362037</v>
       </c>
       <c r="J18" s="34">
-        <v>186825.92</v>
+        <v>192500</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.46294041184685664</v>
-      </c>
-      <c r="M18" s="56"/>
-      <c r="N18" s="56"/>
-      <c r="O18" s="56"/>
-      <c r="P18" s="56"/>
-      <c r="Q18" s="56"/>
-      <c r="R18" s="56"/>
-      <c r="S18" s="56"/>
-      <c r="T18" s="56"/>
-      <c r="U18" s="56"/>
-      <c r="V18" s="56"/>
-    </row>
-    <row r="19" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.46828639061753352</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
         <v>11</v>
       </c>
@@ -1585,43 +1412,33 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.2E-2</v>
+        <v>6.0299999999999999E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-8.0000000000000071E-3</v>
+        <v>-9.7000000000000072E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.11428571428571438</v>
+        <v>-0.13857142857142865</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>1996601.5299999998</v>
+        <v>2167950</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1760197.67</v>
+        <v>1773325</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.11840312473365677</v>
-      </c>
-      <c r="M19" s="56"/>
-      <c r="N19" s="56"/>
-      <c r="O19" s="56"/>
-      <c r="P19" s="56"/>
-      <c r="Q19" s="56"/>
-      <c r="R19" s="56"/>
-      <c r="S19" s="56"/>
-      <c r="T19" s="56"/>
-      <c r="U19" s="56"/>
-      <c r="V19" s="56"/>
-    </row>
-    <row r="20" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.18202679951105882</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B20" s="36" t="s">
         <v>13</v>
       </c>
@@ -1641,105 +1458,75 @@
         <v>0.58908382066276799</v>
       </c>
       <c r="K20" s="44"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="56"/>
-      <c r="P20" s="56"/>
-      <c r="Q20" s="56"/>
-      <c r="R20" s="56"/>
-      <c r="S20" s="56"/>
-      <c r="T20" s="56"/>
-      <c r="U20" s="56"/>
-      <c r="V20" s="56"/>
-    </row>
-    <row r="21" spans="2:22" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="2:11" ht="20.399999999999999" x14ac:dyDescent="0.3">
       <c r="B21" s="13" t="s">
         <v>14</v>
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>377.41935483870969</v>
+        <v>415.16129032258067</v>
       </c>
       <c r="D21" s="45">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-113.41935483870969</v>
+        <v>-149.16129032258067</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.30051282051282052</v>
-      </c>
-      <c r="H21" s="59" t="s">
+        <v>-0.35928515928515931</v>
+      </c>
+      <c r="H21" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="59"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="M21" s="56"/>
-      <c r="N21" s="56"/>
-      <c r="O21" s="56"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="56"/>
-      <c r="R21" s="56"/>
-      <c r="S21" s="56"/>
-      <c r="T21" s="56"/>
-      <c r="U21" s="56"/>
-      <c r="V21" s="56"/>
-    </row>
-    <row r="22" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+    </row>
+    <row r="22" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B22" s="36" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>754.83870967741939</v>
+        <v>830.32258064516134</v>
       </c>
       <c r="D22" s="47">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-322.83870967741939</v>
+        <v>-395.32258064516134</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.4276923076923077</v>
-      </c>
-      <c r="M22" s="56"/>
-      <c r="N22" s="56"/>
-      <c r="O22" s="56"/>
-      <c r="P22" s="56"/>
-      <c r="Q22" s="56"/>
-      <c r="R22" s="56"/>
-      <c r="S22" s="56"/>
-      <c r="T22" s="56"/>
-      <c r="U22" s="56"/>
-      <c r="V22" s="56"/>
-    </row>
-    <row r="23" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>-0.47610722610722611</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B23" s="13" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>5526.4516129032254</v>
+        <v>6079.0967741935483</v>
       </c>
       <c r="D23" s="45">
-        <v>4257</v>
+        <v>4414</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1269.4516129032254</v>
+        <v>-1665.0967741935483</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.22970464627597473</v>
+        <v>-0.27390529153312249</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46316</v>
+        <v>46318</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1747,18 +1534,8 @@
       <c r="J23" s="9">
         <v>2026</v>
       </c>
-      <c r="M23" s="56"/>
-      <c r="N23" s="56"/>
-      <c r="O23" s="56"/>
-      <c r="P23" s="56"/>
-      <c r="Q23" s="56"/>
-      <c r="R23" s="56"/>
-      <c r="S23" s="56"/>
-      <c r="T23" s="56"/>
-      <c r="U23" s="56"/>
-      <c r="V23" s="56"/>
-    </row>
-    <row r="24" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
@@ -1768,29 +1545,19 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1655</v>
+        <v>1631</v>
       </c>
       <c r="J24" s="49">
-        <v>1469</v>
-      </c>
-      <c r="M24" s="56"/>
-      <c r="N24" s="56"/>
-      <c r="O24" s="56"/>
-      <c r="P24" s="56"/>
-      <c r="Q24" s="56"/>
-      <c r="R24" s="56"/>
-      <c r="S24" s="56"/>
-      <c r="T24" s="56"/>
-      <c r="U24" s="56"/>
-      <c r="V24" s="56"/>
-    </row>
-    <row r="25" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="B25" s="50" t="s">
         <v>30</v>
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2729077.25</v>
+        <v>2498654.9545454541</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1798,131 +1565,41 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.90969241666666667</v>
+        <v>0.83288498484848472</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2597</v>
+        <v>2555</v>
       </c>
       <c r="J25" s="52">
-        <v>3312</v>
-      </c>
-      <c r="M25" s="56"/>
-      <c r="N25" s="56"/>
-      <c r="O25" s="56"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="56"/>
-      <c r="R25" s="56"/>
-      <c r="S25" s="56"/>
-      <c r="T25" s="56"/>
-      <c r="U25" s="56"/>
-      <c r="V25" s="56"/>
-    </row>
-    <row r="26" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="H26" s="29" t="s">
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="J26" s="49">
         <v>412</v>
       </c>
-      <c r="M26" s="56"/>
-      <c r="N26" s="56"/>
-      <c r="O26" s="56"/>
-      <c r="P26" s="56"/>
-      <c r="Q26" s="56"/>
-      <c r="R26" s="56"/>
-      <c r="S26" s="56"/>
-      <c r="T26" s="56"/>
-      <c r="U26" s="56"/>
-      <c r="V26" s="56"/>
-    </row>
-    <row r="27" spans="2:22" ht="18.600000000000001" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
       <c r="H27" s="11" t="s">
         <v>27</v>
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4549</v>
+        <v>4480</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5193</v>
-      </c>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="56"/>
-      <c r="S27" s="56"/>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-    </row>
-    <row r="28" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="M28" s="56"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="56"/>
-      <c r="P28" s="56"/>
-      <c r="Q28" s="56"/>
-      <c r="R28" s="56"/>
-      <c r="S28" s="56"/>
-      <c r="T28" s="56"/>
-      <c r="U28" s="56"/>
-      <c r="V28" s="56"/>
-    </row>
-    <row r="29" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="M29" s="56"/>
-      <c r="N29" s="56"/>
-      <c r="O29" s="56"/>
-      <c r="P29" s="56"/>
-      <c r="Q29" s="56"/>
-      <c r="R29" s="56"/>
-      <c r="S29" s="56"/>
-      <c r="T29" s="56"/>
-      <c r="U29" s="56"/>
-      <c r="V29" s="56"/>
-    </row>
-    <row r="30" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="M30" s="56"/>
-      <c r="N30" s="56"/>
-      <c r="O30" s="56"/>
-      <c r="P30" s="56"/>
-      <c r="Q30" s="56"/>
-      <c r="R30" s="56"/>
-      <c r="S30" s="56"/>
-      <c r="T30" s="56"/>
-      <c r="U30" s="56"/>
-      <c r="V30" s="56"/>
-    </row>
-    <row r="31" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="M31" s="56"/>
-      <c r="N31" s="56"/>
-      <c r="O31" s="56"/>
-      <c r="P31" s="56"/>
-      <c r="Q31" s="56"/>
-      <c r="R31" s="56"/>
-      <c r="S31" s="56"/>
-      <c r="T31" s="56"/>
-      <c r="U31" s="56"/>
-      <c r="V31" s="56"/>
-    </row>
-    <row r="32" spans="2:22" x14ac:dyDescent="0.3">
-      <c r="M32" s="56"/>
-      <c r="N32" s="56"/>
-      <c r="O32" s="56"/>
-      <c r="P32" s="56"/>
-      <c r="Q32" s="56"/>
-      <c r="R32" s="56"/>
-      <c r="S32" s="56"/>
-      <c r="T32" s="56"/>
-      <c r="U32" s="56"/>
-      <c r="V32" s="56"/>
+        <v>5112</v>
+      </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="53"/>
@@ -1931,8 +1608,7 @@
       <c r="F33" s="55"/>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="M2:V32"/>
+  <mergeCells count="8">
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="H21:K21"/>
     <mergeCell ref="B2:E2"/>

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F771AF7-B270-478A-B9A5-B8FB922B1EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AB6249-789A-4B20-9785-D93C0852E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1071,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>966530</v>
+        <v>986768.63</v>
       </c>
       <c r="J5" s="14">
-        <v>689858</v>
+        <v>692138</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.28625288402843163</v>
+        <v>-0.29858126924849648</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1134,10 +1134,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>1139590</v>
+        <v>1172442.98</v>
       </c>
       <c r="J8" s="14">
-        <v>1022206</v>
+        <v>1030885</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-0.1030054668784387</v>
+        <v>-0.12073762427235479</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1211,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>61359</v>
+        <v>63903.71</v>
       </c>
       <c r="J11" s="14">
-        <v>61677</v>
+        <v>61178</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>5.1826137974868569E-3</v>
+        <v>-4.2653392111349997E-2</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1301,14 +1301,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1457774</v>
+        <v>1497035.63</v>
       </c>
       <c r="J15" s="30">
-        <v>1295218</v>
+        <v>1306178.93</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-0.11150974019292426</v>
+        <v>-0.12748975119583494</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,14 +1331,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>348139</v>
+        <v>352516.1</v>
       </c>
       <c r="J16" s="34">
-        <v>285607</v>
+        <v>285607.40000000002</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-0.17961791123660376</v>
+        <v>-0.18980324586593333</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>2129032.2580645159</v>
+        <v>2225806.4516129033</v>
       </c>
       <c r="D17" s="35">
-        <v>1773239</v>
+        <v>1784200</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-355793.25806451589</v>
+        <v>-441606.45161290327</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.16711501515151506</v>
+        <v>-0.19840289855072465</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1393,14 +1393,14 @@
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>362037</v>
+        <v>373563.59</v>
       </c>
       <c r="J18" s="34">
-        <v>192500</v>
+        <v>191917</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.46828639061753352</v>
+        <v>-0.48625346490539945</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1412,30 +1412,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.0299999999999999E-2</v>
+        <v>5.9400000000000001E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-9.7000000000000072E-3</v>
+        <v>-1.0600000000000005E-2</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.13857142857142865</v>
+        <v>-0.1514285714285715</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>2167950</v>
+        <v>2223115.3199999998</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1773325</v>
+        <v>1783703.33</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.18202679951105882</v>
+        <v>-0.19765595875611153</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1447,15 +1447,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4076</v>
+        <v>4064</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1511</v>
+        <v>1499</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.58908382066276799</v>
+        <v>0.58440545808966859</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1465,18 +1465,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>415.16129032258067</v>
+        <v>434.03225806451616</v>
       </c>
       <c r="D21" s="45">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-149.16129032258067</v>
+        <v>-166.03225806451616</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.35928515928515931</v>
+        <v>-0.38253437383872169</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1491,18 +1491,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>830.32258064516134</v>
+        <v>868.06451612903231</v>
       </c>
       <c r="D22" s="47">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-395.32258064516134</v>
+        <v>-429.06451612903231</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.47610722610722611</v>
+        <v>-0.49427722036417693</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>6079.0967741935483</v>
+        <v>6355.4193548387093</v>
       </c>
       <c r="D23" s="45">
-        <v>4414</v>
+        <v>4515</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1665.0967741935483</v>
+        <v>-1840.4193548387093</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.27390529153312249</v>
+        <v>-0.28958267772487789</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1545,10 +1545,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1631</v>
+        <v>1635</v>
       </c>
       <c r="J24" s="49">
-        <v>1460</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2498654.9545454541</v>
+        <v>2404791.3043478262</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,16 +1565,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.83288498484848472</v>
+        <v>0.80159710144927543</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="J25" s="52">
-        <v>3240</v>
+        <v>3251</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4480</v>
+        <v>4486</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5112</v>
+        <v>5125</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AB6249-789A-4B20-9785-D93C0852E1A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998970B8-17DE-4112-B319-0F87256DE0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1074,7 +1074,7 @@
         <v>986768.63</v>
       </c>
       <c r="J5" s="14">
-        <v>692138</v>
+        <v>719281</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.29858126924849648</v>
+        <v>-0.27107431455335174</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1137,7 +1137,7 @@
         <v>1172442.98</v>
       </c>
       <c r="J8" s="14">
-        <v>1030885</v>
+        <v>1107547</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-0.12073762427235479</v>
+        <v>-5.5351075580664877E-2</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1214,7 +1214,7 @@
         <v>63903.71</v>
       </c>
       <c r="J11" s="14">
-        <v>61178</v>
+        <v>65358</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>-4.2653392111349997E-2</v>
+        <v>2.2757520650992014E-2</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1301,14 +1301,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1497035.63</v>
+        <v>1520939</v>
       </c>
       <c r="J15" s="30">
-        <v>1306178.93</v>
+        <v>1402892.56</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-0.12748975119583494</v>
+        <v>-7.761418439529788E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,14 +1331,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>352516.1</v>
+        <v>352516</v>
       </c>
       <c r="J16" s="34">
-        <v>285607.40000000002</v>
+        <v>289606.49</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-0.18980324586593333</v>
+        <v>-0.17845859478718695</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>2225806.4516129033</v>
+        <v>2322580.6451612902</v>
       </c>
       <c r="D17" s="35">
-        <v>1784200</v>
+        <v>1892185</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-441606.45161290327</v>
+        <v>-430395.64516129019</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.19840289855072465</v>
+        <v>-0.18530923611111105</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1379,28 +1379,28 @@
         <v>1.8</v>
       </c>
       <c r="D18" s="38">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.16000000000000014</v>
+        <v>-0.17000000000000015</v>
       </c>
       <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-8.8888888888888962E-2</v>
+        <v>-9.4444444444444525E-2</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>373563.59</v>
+        <v>380669.28</v>
       </c>
       <c r="J18" s="34">
-        <v>191917</v>
+        <v>199771.98</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.48625346490539945</v>
+        <v>-0.47520855898852676</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1412,30 +1412,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>5.9400000000000001E-2</v>
+        <v>5.9499999999999997E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-1.0600000000000005E-2</v>
+        <v>-1.0500000000000009E-2</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.1514285714285715</v>
+        <v>-0.15000000000000011</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>2223115.3199999998</v>
+        <v>2254124.2800000003</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1783703.33</v>
+        <v>1892271.03</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.19765595875611153</v>
+        <v>-0.1605294141102106</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1447,15 +1447,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4064</v>
+        <v>4060</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1499</v>
+        <v>1495</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.58440545808966859</v>
+        <v>0.5828460038986355</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1465,18 +1465,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>434.03225806451616</v>
+        <v>452.90322580645159</v>
       </c>
       <c r="D21" s="45">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-166.03225806451616</v>
+        <v>-166.90322580645159</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.38253437383872169</v>
+        <v>-0.36851851851851847</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1491,18 +1491,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>868.06451612903231</v>
+        <v>905.80645161290317</v>
       </c>
       <c r="D22" s="47">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-429.06451612903231</v>
+        <v>-439.80645161290317</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.49427722036417693</v>
+        <v>-0.4855413105413105</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>6355.4193548387093</v>
+        <v>6631.7419354838712</v>
       </c>
       <c r="D23" s="45">
-        <v>4515</v>
+        <v>4805</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1840.4193548387093</v>
+        <v>-1826.7419354838712</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.28958267772487789</v>
+        <v>-0.27545431551093474</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1545,10 +1545,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1635</v>
+        <v>1615</v>
       </c>
       <c r="J24" s="49">
-        <v>1462</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2404791.3043478262</v>
+        <v>2444072.291666667</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,16 +1565,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.80159710144927543</v>
+        <v>0.81469076388888895</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2557</v>
+        <v>2502</v>
       </c>
       <c r="J25" s="52">
-        <v>3251</v>
+        <v>3221</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1582,10 +1582,10 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="J26" s="49">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4486</v>
+        <v>4401</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5125</v>
+        <v>5084</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998970B8-17DE-4112-B319-0F87256DE0AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6AA71C-4D4D-47E4-A225-D5D673492FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1074,7 +1074,7 @@
         <v>986768.63</v>
       </c>
       <c r="J5" s="14">
-        <v>719281</v>
+        <v>799504</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.27107431455335174</v>
+        <v>-0.18977562146457783</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1137,7 +1137,7 @@
         <v>1172442.98</v>
       </c>
       <c r="J8" s="14">
-        <v>1107547</v>
+        <v>117549</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-5.5351075580664877E-2</v>
+        <v>-0.89974011358744288</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1214,7 +1214,7 @@
         <v>63903.71</v>
       </c>
       <c r="J11" s="14">
-        <v>65358</v>
+        <v>70737</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>2.2757520650992014E-2</v>
+        <v>0.10693103733726894</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1301,14 +1301,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1520939</v>
+        <v>1638468</v>
       </c>
       <c r="J15" s="30">
-        <v>1402892.56</v>
+        <v>1507305.52</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-7.761418439529788E-2</v>
+        <v>-8.0051902142733278E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,14 +1331,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>352516</v>
+        <v>381075</v>
       </c>
       <c r="J16" s="34">
-        <v>289606.49</v>
+        <v>331920</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-0.17845859478718695</v>
+        <v>-0.12899035622908872</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>2322580.6451612902</v>
+        <v>2419354.8387096771</v>
       </c>
       <c r="D17" s="35">
-        <v>1892185</v>
+        <v>2045700</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-430395.64516129019</v>
+        <v>-373654.8387096771</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.18530923611111105</v>
+        <v>-0.15444399999999989</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1379,28 +1379,28 @@
         <v>1.8</v>
       </c>
       <c r="D18" s="38">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.17000000000000015</v>
+        <v>-0.16000000000000014</v>
       </c>
       <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-9.4444444444444525E-2</v>
+        <v>-8.8888888888888962E-2</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>380669.28</v>
+        <v>414083</v>
       </c>
       <c r="J18" s="34">
-        <v>199771.98</v>
+        <v>216718</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.47520855898852676</v>
+        <v>-0.47663149658401816</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1427,15 +1427,15 @@
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>2254124.2800000003</v>
+        <v>2433626</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>1892271.03</v>
+        <v>2055943.52</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.1605294141102106</v>
+        <v>-0.1551933123659921</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1447,15 +1447,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4060</v>
+        <v>4075</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1495</v>
+        <v>1510</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.5828460038986355</v>
+        <v>0.58869395711500971</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1465,18 +1465,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>452.90322580645159</v>
+        <v>471.77419354838707</v>
       </c>
       <c r="D21" s="45">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-166.90322580645159</v>
+        <v>-164.77419354838707</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.36851851851851847</v>
+        <v>-0.34926495726495721</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1491,18 +1491,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>905.80645161290317</v>
+        <v>943.54838709677415</v>
       </c>
       <c r="D22" s="47">
-        <v>466</v>
+        <v>502</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-439.80645161290317</v>
+        <v>-441.54838709677415</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.4855413105413105</v>
+        <v>-0.46796581196581194</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>6631.7419354838712</v>
+        <v>6908.0645161290322</v>
       </c>
       <c r="D23" s="45">
-        <v>4805</v>
+        <v>5173</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1826.7419354838712</v>
+        <v>-1735.0645161290322</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.27545431551093474</v>
+        <v>-0.25116507121176745</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1545,10 +1545,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1615</v>
+        <v>1597</v>
       </c>
       <c r="J24" s="49">
-        <v>1453</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2444072.291666667</v>
+        <v>2536668</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,16 +1565,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.81469076388888895</v>
+        <v>0.84555599999999997</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2502</v>
+        <v>2480</v>
       </c>
       <c r="J25" s="52">
-        <v>3221</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1582,10 +1582,10 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J26" s="49">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4401</v>
+        <v>4358</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5084</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6AA71C-4D4D-47E4-A225-D5D673492FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794105F0-3F42-4B26-8C71-34578EE27781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1071,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>986768.63</v>
+        <v>1098444.81</v>
       </c>
       <c r="J5" s="14">
-        <v>799504</v>
+        <v>833809</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.18977562146457783</v>
+        <v>-0.24091862202890291</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1134,10 +1134,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>1172442.98</v>
+        <v>1372687.53</v>
       </c>
       <c r="J8" s="14">
-        <v>117549</v>
+        <v>1258732</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-0.89974011358744288</v>
+        <v>-8.3016365712887397E-2</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1211,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>63903.71</v>
+        <v>74676.47</v>
       </c>
       <c r="J11" s="14">
-        <v>70737</v>
+        <v>76015</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>0.10693103733726894</v>
+        <v>1.7924387695347654E-2</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1301,14 +1301,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1638468</v>
+        <v>1679056.46</v>
       </c>
       <c r="J15" s="30">
-        <v>1507305.52</v>
+        <v>1589391.52</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-8.0051902142733278E-2</v>
+        <v>-5.3401980300293195E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,14 +1331,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>381075</v>
+        <v>431172.98</v>
       </c>
       <c r="J16" s="34">
-        <v>331920</v>
+        <v>351890.03</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-0.12899035622908872</v>
+        <v>-0.18387736170295266</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>2419354.8387096771</v>
+        <v>2516129.0322580645</v>
       </c>
       <c r="D17" s="35">
-        <v>2045700</v>
+        <v>2168555</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-373654.8387096771</v>
+        <v>-347574.03225806449</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.15444399999999989</v>
+        <v>-0.13813839743589743</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1393,14 +1393,14 @@
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>414083</v>
+        <v>435579.37</v>
       </c>
       <c r="J18" s="34">
-        <v>216718</v>
+        <v>226775.79</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.47663149658401816</v>
+        <v>-0.47936976445877133</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1412,30 +1412,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>5.9499999999999997E-2</v>
+        <v>6.1800000000000001E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-1.0500000000000009E-2</v>
+        <v>-8.2000000000000059E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.15000000000000011</v>
+        <v>-0.11714285714285722</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>2433626</v>
+        <v>2545808.81</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>2055943.52</v>
+        <v>2168057.34</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.1551933123659921</v>
+        <v>-0.14838171213650575</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1447,15 +1447,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4075</v>
+        <v>4061</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1510</v>
+        <v>1496</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.58869395711500971</v>
+        <v>0.58323586744639377</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1465,18 +1465,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>471.77419354838707</v>
+        <v>490.64516129032256</v>
       </c>
       <c r="D21" s="45">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-164.77419354838707</v>
+        <v>-164.64516129032256</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.34926495726495721</v>
+        <v>-0.33556870479947398</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1491,18 +1491,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>943.54838709677415</v>
+        <v>981.29032258064512</v>
       </c>
       <c r="D22" s="47">
-        <v>502</v>
+        <v>534</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-441.54838709677415</v>
+        <v>-447.29032258064512</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.46796581196581194</v>
+        <v>-0.455818540433925</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>6908.0645161290322</v>
+        <v>7184.3870967741932</v>
       </c>
       <c r="D23" s="45">
-        <v>5173</v>
+        <v>5274</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1735.0645161290322</v>
+        <v>-1910.3870967741932</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.25116507121176745</v>
+        <v>-0.26590815208606472</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1545,10 +1545,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="J24" s="49">
-        <v>1437</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2536668</v>
+        <v>2585584.8076923075</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,16 +1565,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.84555599999999997</v>
+        <v>0.86186160256410249</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="J25" s="52">
-        <v>3202</v>
+        <v>3146</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1585,7 +1585,7 @@
         <v>281</v>
       </c>
       <c r="J26" s="49">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4358</v>
+        <v>4360</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>5046</v>
+        <v>4979</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{794105F0-3F42-4B26-8C71-34578EE27781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DF1465-56FC-4298-8CCC-81DEA083ABCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1071,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>1098444.81</v>
+        <v>1098445</v>
       </c>
       <c r="J5" s="14">
-        <v>833809</v>
+        <v>935778</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.24091862202890291</v>
+        <v>-0.14808843410457506</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1134,10 +1134,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>1372687.53</v>
+        <v>1392075</v>
       </c>
       <c r="J8" s="14">
-        <v>1258732</v>
+        <v>1331375</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-8.3016365712887397E-2</v>
+        <v>-4.3603972487114562E-2</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1211,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>74676.47</v>
+        <v>74676</v>
       </c>
       <c r="J11" s="14">
-        <v>76015</v>
+        <v>79877</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>1.7924387695347654E-2</v>
+        <v>6.9647544056992805E-2</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1301,14 +1301,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1679056.46</v>
+        <v>1698444</v>
       </c>
       <c r="J15" s="30">
-        <v>1589391.52</v>
+        <v>1643255</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-5.3401980300293195E-2</v>
+        <v>-3.2493859085139132E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,14 +1331,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>431172.98</v>
+        <v>431173</v>
       </c>
       <c r="J16" s="34">
-        <v>351890.03</v>
+        <v>376822</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-0.18387736170295266</v>
+        <v>-0.12605381134718552</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>2516129.0322580645</v>
+        <v>2612903.2258064514</v>
       </c>
       <c r="D17" s="35">
-        <v>2168555</v>
+        <v>2247354</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-347574.03225806449</v>
+        <v>-365549.2258064514</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.13813839743589743</v>
+        <v>-0.13990155555555547</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1393,14 +1393,14 @@
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>435579.37</v>
+        <v>436489</v>
       </c>
       <c r="J18" s="34">
-        <v>226775.79</v>
+        <v>227443</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.47936976445877133</v>
+        <v>-0.47892615850571263</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1412,30 +1412,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.1800000000000001E-2</v>
+        <v>6.2899999999999998E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-8.2000000000000059E-3</v>
+        <v>-7.1000000000000091E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.11714285714285722</v>
+        <v>-0.10142857142857155</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>2545808.81</v>
+        <v>2566106</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>2168057.34</v>
+        <v>2247520</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.14838171213650575</v>
+        <v>-0.12415153543929991</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1447,15 +1447,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4061</v>
+        <v>4042</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1496</v>
+        <v>1477</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.58323586744639377</v>
+        <v>0.57582846003898636</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1465,18 +1465,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>490.64516129032256</v>
+        <v>509.51612903225805</v>
       </c>
       <c r="D21" s="45">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-164.64516129032256</v>
+        <v>-170.51612903225805</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.33556870479947398</v>
+        <v>-0.33466286799620132</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1491,18 +1491,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>981.29032258064512</v>
+        <v>1019.0322580645161</v>
       </c>
       <c r="D22" s="47">
-        <v>534</v>
+        <v>556</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-447.29032258064512</v>
+        <v>-463.0322580645161</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.455818540433925</v>
+        <v>-0.45438429882874326</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>7184.3870967741932</v>
+        <v>7460.7096774193542</v>
       </c>
       <c r="D23" s="45">
-        <v>5274</v>
+        <v>5390</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1910.3870967741932</v>
+        <v>-2070.7096774193542</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.26590815208606472</v>
+        <v>-0.27754862029902883</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1545,10 +1545,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1598</v>
+        <v>1591</v>
       </c>
       <c r="J24" s="49">
-        <v>1431</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2585584.8076923075</v>
+        <v>2580295.333333333</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,16 +1565,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.86186160256410249</v>
+        <v>0.86009844444444439</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2481</v>
+        <v>2455</v>
       </c>
       <c r="J25" s="52">
-        <v>3146</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1582,10 +1582,10 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J26" s="49">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4360</v>
+        <v>4325</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>4979</v>
+        <v>4941</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5DF1465-56FC-4298-8CCC-81DEA083ABCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9948C154-B829-4D6D-968A-7C22C35BA2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1071,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>1098445</v>
+        <v>1139892</v>
       </c>
       <c r="J5" s="14">
-        <v>935778</v>
+        <v>863893</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.14808843410457506</v>
+        <v>-0.24212732434300799</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1134,10 +1134,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>1392075</v>
+        <v>1479424</v>
       </c>
       <c r="J8" s="14">
-        <v>1331375</v>
+        <v>1385583</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-4.3603972487114562E-2</v>
+        <v>-6.3430767650112463E-2</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1211,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>74676</v>
+        <v>80840</v>
       </c>
       <c r="J11" s="14">
-        <v>79877</v>
+        <v>81908</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>6.9647544056992805E-2</v>
+        <v>1.3211281543790143E-2</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1301,14 +1301,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1698444</v>
+        <v>1782152</v>
       </c>
       <c r="J15" s="30">
-        <v>1643255</v>
+        <v>1701848</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-3.2493859085139132E-2</v>
+        <v>-4.506012955123917E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,14 +1331,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>431173</v>
+        <v>464449</v>
       </c>
       <c r="J16" s="34">
-        <v>376822</v>
+        <v>395142</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-0.12605381134718552</v>
+        <v>-0.14922413440442328</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1350,15 +1350,15 @@
         <v>2612903.2258064514</v>
       </c>
       <c r="D17" s="35">
-        <v>2247354</v>
+        <v>2331384</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-365549.2258064514</v>
+        <v>-281519.2258064514</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.13990155555555547</v>
+        <v>-0.10774192592592585</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1379,28 +1379,28 @@
         <v>1.8</v>
       </c>
       <c r="D18" s="38">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.16000000000000014</v>
+        <v>-0.15000000000000013</v>
       </c>
       <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-8.8888888888888962E-2</v>
+        <v>-8.3333333333333412E-2</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>436489</v>
+        <v>454466</v>
       </c>
       <c r="J18" s="34">
-        <v>227443</v>
+        <v>234559</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.47892615850571263</v>
+        <v>-0.48387998222089224</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1412,30 +1412,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.2899999999999998E-2</v>
+        <v>6.3E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-7.1000000000000091E-3</v>
+        <v>-7.0000000000000062E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.10142857142857155</v>
+        <v>-0.10000000000000007</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>2566106</v>
+        <v>2701067</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>2247520</v>
+        <v>2331549</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.12415153543929991</v>
+        <v>-0.1368044554244674</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1447,15 +1447,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4042</v>
+        <v>4012</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1477</v>
+        <v>1447</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.57582846003898636</v>
+        <v>0.56413255360623782</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1468,15 +1468,15 @@
         <v>509.51612903225805</v>
       </c>
       <c r="D21" s="45">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-170.51612903225805</v>
+        <v>-156.51612903225805</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.33466286799620132</v>
+        <v>-0.30718581829692937</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1494,15 +1494,15 @@
         <v>1019.0322580645161</v>
       </c>
       <c r="D22" s="47">
-        <v>556</v>
+        <v>581</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-463.0322580645161</v>
+        <v>-438.0322580645161</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.45438429882874326</v>
+        <v>-0.42985121874010762</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1514,19 +1514,19 @@
         <v>7460.7096774193542</v>
       </c>
       <c r="D23" s="45">
-        <v>5390</v>
+        <v>5616</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-2070.7096774193542</v>
+        <v>-1844.7096774193542</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.27754862029902883</v>
+        <v>-0.24725659584403448</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1545,10 +1545,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1591</v>
+        <v>1588</v>
       </c>
       <c r="J24" s="49">
-        <v>1423</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2580295.333333333</v>
+        <v>2676774.2222222225</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,16 +1565,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.86009844444444439</v>
+        <v>0.8922580740740742</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2455</v>
+        <v>2442</v>
       </c>
       <c r="J25" s="52">
-        <v>3118</v>
+        <v>3104</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1582,10 +1582,10 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="J26" s="49">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4325</v>
+        <v>4307</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>4941</v>
+        <v>4923</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9948C154-B829-4D6D-968A-7C22C35BA2FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4F6BD7-8C8D-413B-858B-74F784B21651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>2612903.2258064514</v>
+        <v>2709677.4193548383</v>
       </c>
       <c r="D17" s="35">
         <v>2331384</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-281519.2258064514</v>
+        <v>-378293.41935483832</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.10774192592592585</v>
+        <v>-0.1396082857142856</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1465,18 +1465,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>509.51612903225805</v>
+        <v>528.38709677419354</v>
       </c>
       <c r="D21" s="45">
         <v>353</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-156.51612903225805</v>
+        <v>-175.38709677419354</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.30718581829692937</v>
+        <v>-0.33192918192918192</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1491,18 +1491,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>1019.0322580645161</v>
+        <v>1056.7741935483871</v>
       </c>
       <c r="D22" s="47">
         <v>581</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-438.0322580645161</v>
+        <v>-475.77419354838707</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.42985121874010762</v>
+        <v>-0.45021367521367522</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1511,18 +1511,18 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>7460.7096774193542</v>
+        <v>7737.0322580645161</v>
       </c>
       <c r="D23" s="45">
         <v>5616</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-1844.7096774193542</v>
+        <v>-2121.0322580645161</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.24725659584403448</v>
+        <v>-0.27414028884960473</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2676774.2222222225</v>
+        <v>2581175.1428571432</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.8922580740740742</v>
+        <v>0.86039171428571437</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>

--- a/Ekim 2026 Data.xlsx
+++ b/Ekim 2026 Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\UYGULAMA İÇİN GEREKLİ DOSYALAR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\magaza.mudur\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4F6BD7-8C8D-413B-858B-74F784B21651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C155FC-FCB7-4098-BB18-4E9C54296AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1062,7 +1062,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="12">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
@@ -1071,10 +1071,10 @@
         <v>5</v>
       </c>
       <c r="I5" s="14">
-        <v>1139892</v>
+        <v>1150175</v>
       </c>
       <c r="J5" s="14">
-        <v>863893</v>
+        <v>916648</v>
       </c>
       <c r="K5" s="10"/>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="I6" s="56">
         <f>J5/I5-1</f>
-        <v>-0.24212732434300799</v>
+        <v>-0.20303605973004113</v>
       </c>
       <c r="J6" s="57"/>
       <c r="K6" s="10"/>
@@ -1134,10 +1134,10 @@
         <v>5</v>
       </c>
       <c r="I8" s="14">
-        <v>1479424</v>
+        <v>1504861.01</v>
       </c>
       <c r="J8" s="14">
-        <v>1385583</v>
+        <v>1512846</v>
       </c>
       <c r="K8" s="10"/>
     </row>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I9" s="56">
         <f>J8/I8-1</f>
-        <v>-6.3430767650112463E-2</v>
+        <v>5.3061312286906137E-3</v>
       </c>
       <c r="J9" s="57"/>
       <c r="K9" s="10"/>
@@ -1211,10 +1211,10 @@
         <v>5</v>
       </c>
       <c r="I11" s="14">
-        <v>80840</v>
+        <v>80840.179999999993</v>
       </c>
       <c r="J11" s="14">
-        <v>81908</v>
+        <v>85207</v>
       </c>
       <c r="K11" s="10"/>
     </row>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I12" s="56">
         <f>J11/I11-1</f>
-        <v>1.3211281543790143E-2</v>
+        <v>5.4017940088703531E-2</v>
       </c>
       <c r="J12" s="57"/>
       <c r="K12" s="10"/>
@@ -1301,14 +1301,14 @@
         <v>18</v>
       </c>
       <c r="I15" s="30">
-        <v>1782152</v>
+        <v>1811145.39</v>
       </c>
       <c r="J15" s="30">
-        <v>1701848</v>
+        <v>1830825.18</v>
       </c>
       <c r="K15" s="31">
         <f>J15/I15-1</f>
-        <v>-4.506012955123917E-2</v>
+        <v>1.0865936058286341E-2</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="19.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1331,14 +1331,14 @@
         <v>24</v>
       </c>
       <c r="I16" s="34">
-        <v>464449</v>
+        <v>471174.78</v>
       </c>
       <c r="J16" s="34">
-        <v>395142</v>
+        <v>422361.02</v>
       </c>
       <c r="K16" s="31">
         <f>J16/I16-1</f>
-        <v>-0.14922413440442328</v>
+        <v>-0.10360011204334829</v>
       </c>
     </row>
     <row r="17" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1347,18 +1347,18 @@
       </c>
       <c r="C17" s="16">
         <f>F8*C$5</f>
-        <v>2709677.4193548383</v>
+        <v>2903225.8064516126</v>
       </c>
       <c r="D17" s="35">
-        <v>2331384</v>
+        <v>2514701</v>
       </c>
       <c r="E17" s="16">
         <f t="shared" ref="E17:E23" si="0">D17-C17</f>
-        <v>-378293.41935483832</v>
+        <v>-388524.80645161262</v>
       </c>
       <c r="F17" s="21">
         <f>E17/C17</f>
-        <v>-0.1396082857142856</v>
+        <v>-0.13382521111111104</v>
       </c>
       <c r="H17" s="29" t="s">
         <v>25</v>
@@ -1379,28 +1379,28 @@
         <v>1.8</v>
       </c>
       <c r="D18" s="38">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="E18" s="37">
         <f t="shared" si="0"/>
-        <v>-0.15000000000000013</v>
+        <v>-0.12000000000000011</v>
       </c>
       <c r="F18" s="39">
         <f>(D18-C18)/C18</f>
-        <v>-8.3333333333333412E-2</v>
+        <v>-6.6666666666666721E-2</v>
       </c>
       <c r="H18" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I18" s="34">
-        <v>454466</v>
+        <v>453556.02</v>
       </c>
       <c r="J18" s="34">
-        <v>234559</v>
+        <v>260713.77</v>
       </c>
       <c r="K18" s="31">
         <f>J18/I18-1</f>
-        <v>-0.48387998222089224</v>
+        <v>-0.42517845976336066</v>
       </c>
     </row>
     <row r="19" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1412,30 +1412,30 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D19" s="40">
-        <v>6.3E-2</v>
+        <v>6.2E-2</v>
       </c>
       <c r="E19" s="21">
         <f t="shared" si="0"/>
-        <v>-7.0000000000000062E-3</v>
+        <v>-8.0000000000000071E-3</v>
       </c>
       <c r="F19" s="21">
         <f>(D19-C19)/C19</f>
-        <v>-0.10000000000000007</v>
+        <v>-0.11428571428571438</v>
       </c>
       <c r="H19" s="29" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="41">
         <f>SUM(I15:I18)</f>
-        <v>2701067</v>
+        <v>2735876.19</v>
       </c>
       <c r="J19" s="41">
         <f>SUM(J15:J18)</f>
-        <v>2331549</v>
+        <v>2513899.9700000002</v>
       </c>
       <c r="K19" s="31">
         <f>J19/I19-1</f>
-        <v>-0.1368044554244674</v>
+        <v>-8.113533090837699E-2</v>
       </c>
     </row>
     <row r="20" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1447,15 +1447,15 @@
         <v>2565</v>
       </c>
       <c r="D20" s="43">
-        <v>4012</v>
+        <v>6670</v>
       </c>
       <c r="E20" s="42">
         <f t="shared" si="0"/>
-        <v>1447</v>
+        <v>4105</v>
       </c>
       <c r="F20" s="39">
         <f>(D20-C20)/C20</f>
-        <v>0.56413255360623782</v>
+        <v>1.6003898635477583</v>
       </c>
       <c r="K20" s="44"/>
     </row>
@@ -1465,18 +1465,18 @@
       </c>
       <c r="C21" s="25">
         <f>F12*C$5</f>
-        <v>528.38709677419354</v>
+        <v>566.12903225806451</v>
       </c>
       <c r="D21" s="45">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="E21" s="25">
         <f t="shared" si="0"/>
-        <v>-175.38709677419354</v>
+        <v>-189.12903225806451</v>
       </c>
       <c r="F21" s="21">
         <f>E21/C21</f>
-        <v>-0.33192918192918192</v>
+        <v>-0.33407407407407408</v>
       </c>
       <c r="H21" s="58" t="s">
         <v>28</v>
@@ -1491,18 +1491,18 @@
       </c>
       <c r="C22" s="46">
         <f>F13*C$5</f>
-        <v>1056.7741935483871</v>
+        <v>1132.258064516129</v>
       </c>
       <c r="D22" s="47">
-        <v>581</v>
+        <v>632</v>
       </c>
       <c r="E22" s="46">
         <f t="shared" si="0"/>
-        <v>-475.77419354838707</v>
+        <v>-500.25806451612902</v>
       </c>
       <c r="F22" s="39">
         <f>E22/C22</f>
-        <v>-0.45021367521367522</v>
+        <v>-0.44182336182336179</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1511,22 +1511,22 @@
       </c>
       <c r="C23" s="25">
         <f>F14*C$5</f>
-        <v>7737.0322580645161</v>
+        <v>8289.677419354839</v>
       </c>
       <c r="D23" s="45">
-        <v>5616</v>
+        <v>6077</v>
       </c>
       <c r="E23" s="25">
         <f t="shared" si="0"/>
-        <v>-2121.0322580645161</v>
+        <v>-2212.677419354839</v>
       </c>
       <c r="F23" s="21">
         <f>E23/C23</f>
-        <v>-0.27414028884960473</v>
+        <v>-0.26691960463849329</v>
       </c>
       <c r="H23" s="48">
         <f ca="1">TODAY()</f>
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="I23" s="9">
         <v>2025</v>
@@ -1545,10 +1545,10 @@
         <v>29</v>
       </c>
       <c r="I24" s="49">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="J24" s="49">
-        <v>1421</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C25" s="51">
         <f>(D17/C$5)*C$4</f>
-        <v>2581175.1428571432</v>
+        <v>2598524.3666666667</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="50" t="s">
@@ -1565,16 +1565,16 @@
       </c>
       <c r="F25" s="31">
         <f>C25/C8</f>
-        <v>0.86039171428571437</v>
+        <v>0.86617478888888888</v>
       </c>
       <c r="H25" s="11" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="12">
-        <v>2442</v>
+        <v>2427</v>
       </c>
       <c r="J25" s="52">
-        <v>3104</v>
+        <v>3073</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1582,10 +1582,10 @@
         <v>33</v>
       </c>
       <c r="I26" s="49">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J26" s="49">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="18.600000000000001" x14ac:dyDescent="0.3">
@@ -1594,11 +1594,11 @@
       </c>
       <c r="I27" s="11">
         <f>SUM(I24:I26)</f>
-        <v>4307</v>
+        <v>4289</v>
       </c>
       <c r="J27" s="11">
         <f>SUM(J24:J26)</f>
-        <v>4923</v>
+        <v>4880</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
